--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484685_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484685_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.0967</v>
+        <v>3.6122</v>
       </c>
       <c r="E2" t="n">
-        <v>3.7974</v>
+        <v>3.9075</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2993</v>
+        <v>-0.2953</v>
       </c>
       <c r="G2" t="n">
         <v>3.7298</v>
@@ -610,13 +610,13 @@
         <v>1.0995</v>
       </c>
       <c r="S2" t="n">
-        <v>1.0712</v>
+        <v>0.5867</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.0015</v>
+        <v>0.1086</v>
       </c>
       <c r="U2" t="n">
-        <v>1.0727</v>
+        <v>0.4781</v>
       </c>
       <c r="V2" t="n">
         <v>0.945</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>J. SÁEZ GONZÁLEZ</t>
+          <t>G. GONZALEZ GARCIA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.2502</v>
+        <v>1.7342</v>
       </c>
       <c r="E3" t="n">
-        <v>1.2502</v>
+        <v>5.7956</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>-4.0615</v>
       </c>
       <c r="G3" t="n">
-        <v>1.2502</v>
+        <v>-0.3675</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>-5.5192</v>
       </c>
       <c r="I3" t="n">
-        <v>1.2502</v>
+        <v>5.1517</v>
       </c>
       <c r="J3" t="n">
-        <v>1.2502</v>
+        <v>4.2654</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>-1.6879</v>
       </c>
       <c r="L3" t="n">
-        <v>1.2502</v>
+        <v>5.9534</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>-4.6329</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>-3.8312</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>-0.8017</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>1.4661</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-0.1833</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.6493</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>0.6356000000000001</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>0.4465</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>0.1891</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.267</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>-1.267</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. ALMONACID RUBIO</t>
+          <t>J. SÁEZ GONZÁLEZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.2497</v>
+        <v>1.2502</v>
       </c>
       <c r="E4" t="n">
-        <v>2.4737</v>
+        <v>1.2502</v>
       </c>
       <c r="F4" t="n">
-        <v>-2.2241</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>-5.0838</v>
+        <v>1.2502</v>
       </c>
       <c r="H4" t="n">
-        <v>-3.0612</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>-2.0226</v>
+        <v>1.2502</v>
       </c>
       <c r="J4" t="n">
-        <v>-2.3957</v>
+        <v>1.2502</v>
       </c>
       <c r="K4" t="n">
-        <v>-1.2387</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>-1.157</v>
+        <v>1.2502</v>
       </c>
       <c r="M4" t="n">
-        <v>-2.6881</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.8225</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.8656</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.1833</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0.1833</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>2.4776</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>2.1969</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2808</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>2.8559</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>2.8559</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. DIAGO ROS</t>
+          <t>G. PARDO GALLENT</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1068</v>
+        <v>0.1612</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1371</v>
+        <v>0.3753</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.0303</v>
+        <v>-0.2141</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.112</v>
+        <v>0.1318</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.0062</v>
+        <v>-0.2079</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8943</v>
+        <v>0.3398</v>
       </c>
       <c r="J5" t="n">
-        <v>0.2117</v>
+        <v>0.4952</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0867</v>
+        <v>0.4118</v>
       </c>
       <c r="L5" t="n">
-        <v>0.125</v>
+        <v>0.0833</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.3237</v>
+        <v>-0.3633</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.0929</v>
+        <v>-0.6198</v>
       </c>
       <c r="O5" t="n">
-        <v>0.7692</v>
+        <v>0.2564</v>
       </c>
       <c r="P5" t="n">
-        <v>1.0995</v>
+        <v>0.3665</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-0.1833</v>
       </c>
       <c r="R5" t="n">
-        <v>1.0995</v>
+        <v>0.5498</v>
       </c>
       <c r="S5" t="n">
-        <v>0.3862</v>
+        <v>0.3068</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.0746</v>
+        <v>0.0634</v>
       </c>
       <c r="U5" t="n">
-        <v>0.4608</v>
+        <v>0.2434</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.267</v>
+        <v>-0.6439</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.267</v>
+        <v>-0.6439</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>G. PARDO GALLENT</t>
+          <t>A. DIAGO ROS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0204</v>
+        <v>-0.0002</v>
       </c>
       <c r="E6" t="n">
-        <v>0.4575</v>
+        <v>0.0549</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.437</v>
+        <v>-0.055</v>
       </c>
       <c r="G6" t="n">
-        <v>0.1318</v>
+        <v>-0.112</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.2079</v>
+        <v>-1.0062</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3398</v>
+        <v>0.8943</v>
       </c>
       <c r="J6" t="n">
-        <v>0.4952</v>
+        <v>0.2117</v>
       </c>
       <c r="K6" t="n">
-        <v>0.4118</v>
+        <v>0.0867</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0833</v>
+        <v>0.125</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.3633</v>
+        <v>-0.3237</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.6198</v>
+        <v>-1.0929</v>
       </c>
       <c r="O6" t="n">
-        <v>0.2564</v>
+        <v>0.7692</v>
       </c>
       <c r="P6" t="n">
-        <v>0.3665</v>
+        <v>1.0995</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.1833</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.5498</v>
+        <v>1.0995</v>
       </c>
       <c r="S6" t="n">
-        <v>0.166</v>
+        <v>0.2792</v>
       </c>
       <c r="T6" t="n">
-        <v>0.1456</v>
+        <v>-0.1568</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0204</v>
+        <v>0.4361</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.6439</v>
+        <v>-1.267</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.6439</v>
+        <v>-1.267</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>G. GONZALEZ GARCIA</t>
+          <t>E. VIVANCOS ORTIZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.2644</v>
+        <v>-0.2495</v>
       </c>
       <c r="E7" t="n">
-        <v>4.1191</v>
+        <v>-1.4092</v>
       </c>
       <c r="F7" t="n">
-        <v>-4.3835</v>
+        <v>1.1596</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.3675</v>
+        <v>-1.001</v>
       </c>
       <c r="H7" t="n">
-        <v>-5.5192</v>
+        <v>0.2906</v>
       </c>
       <c r="I7" t="n">
-        <v>5.1517</v>
+        <v>-1.2916</v>
       </c>
       <c r="J7" t="n">
-        <v>4.2654</v>
+        <v>-1.0879</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.6879</v>
+        <v>0.0433</v>
       </c>
       <c r="L7" t="n">
-        <v>5.9534</v>
+        <v>-1.1313</v>
       </c>
       <c r="M7" t="n">
-        <v>-4.6329</v>
+        <v>0.08690000000000001</v>
       </c>
       <c r="N7" t="n">
-        <v>-3.8312</v>
+        <v>0.2472</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.8017</v>
+        <v>-0.1603</v>
       </c>
       <c r="P7" t="n">
-        <v>1.4661</v>
+        <v>0.733</v>
       </c>
       <c r="Q7" t="n">
         <v>-0.1833</v>
       </c>
       <c r="R7" t="n">
-        <v>1.6493</v>
+        <v>0.9163</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.363</v>
+        <v>0.0185</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.23</v>
+        <v>-0.138</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.133</v>
+        <v>0.1565</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.267</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.267</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>E. VIVANCOS ORTIZ</t>
+          <t>A. ALMONACID RUBIO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,64 +1033,64 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.6015</v>
+        <v>-0.7722</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.7116</v>
+        <v>1.5262</v>
       </c>
       <c r="F8" t="n">
-        <v>1.1101</v>
+        <v>-2.2984</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.001</v>
+        <v>-5.0838</v>
       </c>
       <c r="H8" t="n">
-        <v>0.2906</v>
+        <v>-3.0612</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.2916</v>
+        <v>-2.0226</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.0879</v>
+        <v>-2.3957</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0433</v>
+        <v>-1.2387</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.1313</v>
+        <v>-1.157</v>
       </c>
       <c r="M8" t="n">
-        <v>0.08690000000000001</v>
+        <v>-2.6881</v>
       </c>
       <c r="N8" t="n">
-        <v>0.2472</v>
+        <v>-1.8225</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.1603</v>
+        <v>-0.8656</v>
       </c>
       <c r="P8" t="n">
-        <v>0.733</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
         <v>-0.1833</v>
       </c>
       <c r="R8" t="n">
-        <v>0.9163</v>
+        <v>0.1833</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.3335</v>
+        <v>1.4557</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.4404</v>
+        <v>1.2493</v>
       </c>
       <c r="U8" t="n">
-        <v>0.1069</v>
+        <v>0.2064</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>2.8559</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>2.8559</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.126</v>
+        <v>-0.8073</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.6575</v>
+        <v>-0.314</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.4685</v>
+        <v>-0.4933</v>
       </c>
       <c r="G9" t="n">
         <v>-2.3184</v>
@@ -1156,13 +1156,13 @@
         <v>0.733</v>
       </c>
       <c r="S9" t="n">
-        <v>0.4594</v>
+        <v>0.7781</v>
       </c>
       <c r="T9" t="n">
-        <v>0.0536</v>
+        <v>0.3971</v>
       </c>
       <c r="U9" t="n">
-        <v>0.4058</v>
+        <v>0.381</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>J. CASADO SEGURA</t>
+          <t>G. BORREGA BERTOLIN</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.3919</v>
+        <v>-1.5587</v>
       </c>
       <c r="E10" t="n">
-        <v>2.9979</v>
+        <v>0.9357</v>
       </c>
       <c r="F10" t="n">
-        <v>-4.3898</v>
+        <v>-2.4944</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.6355</v>
+        <v>-2.3052</v>
       </c>
       <c r="H10" t="n">
-        <v>-2.1034</v>
+        <v>-2.9818</v>
       </c>
       <c r="I10" t="n">
-        <v>0.468</v>
+        <v>0.6766</v>
       </c>
       <c r="J10" t="n">
-        <v>2.219</v>
+        <v>0.0639</v>
       </c>
       <c r="K10" t="n">
-        <v>0.6929999999999999</v>
+        <v>-0.8052</v>
       </c>
       <c r="L10" t="n">
-        <v>1.526</v>
+        <v>0.8691</v>
       </c>
       <c r="M10" t="n">
-        <v>-3.8545</v>
+        <v>-2.3691</v>
       </c>
       <c r="N10" t="n">
-        <v>-2.7964</v>
+        <v>-2.1766</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.0581</v>
+        <v>-0.1925</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.2828</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.7489</v>
+        <v>-0.9163</v>
       </c>
       <c r="R10" t="n">
-        <v>1.4661</v>
+        <v>0.9163</v>
       </c>
       <c r="S10" t="n">
-        <v>2.1599</v>
+        <v>0.435</v>
       </c>
       <c r="T10" t="n">
-        <v>2.2504</v>
+        <v>0.5211</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0905</v>
+        <v>-0.0862</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.6335</v>
+        <v>0.3115</v>
       </c>
       <c r="W10" t="n">
-        <v>1.2774</v>
+        <v>1.267</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.9109</v>
+        <v>-0.9554</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>G. BORREGA BERTOLIN</t>
+          <t>J. CASADO SEGURA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.941</v>
+        <v>-1.8855</v>
       </c>
       <c r="E11" t="n">
-        <v>0.5782</v>
+        <v>2.2566</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.5192</v>
+        <v>-4.142</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.3052</v>
+        <v>-1.6355</v>
       </c>
       <c r="H11" t="n">
-        <v>-2.9818</v>
+        <v>-2.1034</v>
       </c>
       <c r="I11" t="n">
-        <v>0.6766</v>
+        <v>0.468</v>
       </c>
       <c r="J11" t="n">
-        <v>0.0639</v>
+        <v>2.219</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.8052</v>
+        <v>0.6929999999999999</v>
       </c>
       <c r="L11" t="n">
-        <v>0.8691</v>
+        <v>1.526</v>
       </c>
       <c r="M11" t="n">
-        <v>-2.3691</v>
+        <v>-3.8545</v>
       </c>
       <c r="N11" t="n">
-        <v>-2.1766</v>
+        <v>-2.7964</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.1925</v>
+        <v>-1.0581</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>-1.2828</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.9163</v>
+        <v>-2.7489</v>
       </c>
       <c r="R11" t="n">
-        <v>0.9163</v>
+        <v>1.4661</v>
       </c>
       <c r="S11" t="n">
-        <v>0.0527</v>
+        <v>1.6663</v>
       </c>
       <c r="T11" t="n">
-        <v>0.1637</v>
+        <v>1.5091</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1109</v>
+        <v>0.1572</v>
       </c>
       <c r="V11" t="n">
-        <v>0.3115</v>
+        <v>-0.6335</v>
       </c>
       <c r="W11" t="n">
-        <v>1.267</v>
+        <v>1.2774</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.9554</v>
+        <v>-1.9109</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.6154</v>
+        <v>-2.2693</v>
       </c>
       <c r="E12" t="n">
-        <v>1.1402</v>
+        <v>1.6349</v>
       </c>
       <c r="F12" t="n">
-        <v>-3.7556</v>
+        <v>-3.9043</v>
       </c>
       <c r="G12" t="n">
         <v>-0.7049</v>
@@ -1390,13 +1390,13 @@
         <v>1.2828</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.3374</v>
+        <v>0.008699999999999999</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.101</v>
+        <v>-0.6063</v>
       </c>
       <c r="U12" t="n">
-        <v>0.7635999999999999</v>
+        <v>0.615</v>
       </c>
       <c r="V12" t="n">
         <v>-2.8559</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-2.9512</v>
+        <v>-2.7202</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.9276</v>
+        <v>-1.7213</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.0236</v>
+        <v>-0.9988</v>
       </c>
       <c r="G13" t="n">
         <v>-3.9933</v>
@@ -1468,13 +1468,13 @@
         <v>0.733</v>
       </c>
       <c r="S13" t="n">
-        <v>0.3091</v>
+        <v>0.5402</v>
       </c>
       <c r="T13" t="n">
-        <v>0.0905</v>
+        <v>0.2968</v>
       </c>
       <c r="U13" t="n">
-        <v>0.2186</v>
+        <v>0.2434</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-4.5282</v>
+        <v>-4.539</v>
       </c>
       <c r="E14" t="n">
-        <v>-3.6698</v>
+        <v>-3.6559</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.8583</v>
+        <v>-0.8831</v>
       </c>
       <c r="G14" t="n">
         <v>-4.4002</v>
@@ -1546,13 +1546,13 @@
         <v>1.2828</v>
       </c>
       <c r="S14" t="n">
-        <v>0.8983</v>
+        <v>0.8875</v>
       </c>
       <c r="T14" t="n">
-        <v>0.2172</v>
+        <v>0.2312</v>
       </c>
       <c r="U14" t="n">
-        <v>0.6811</v>
+        <v>0.6563</v>
       </c>
       <c r="V14" t="n">
         <v>0.6231</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-9.695799999999998</v>
+        <v>-8.0441</v>
       </c>
       <c r="E15" t="n">
-        <v>8.984800000000002</v>
+        <v>10.63650000000001</v>
       </c>
       <c r="F15" t="n">
-        <v>-18.6805</v>
+        <v>-18.6806</v>
       </c>
       <c r="G15" t="n">
         <v>-16.81</v>
@@ -1624,16 +1624,16 @@
         <v>11.9117</v>
       </c>
       <c r="S15" t="n">
-        <v>5.946499999999999</v>
+        <v>7.598299999999999</v>
       </c>
       <c r="T15" t="n">
-        <v>2.2704</v>
+        <v>3.922</v>
       </c>
       <c r="U15" t="n">
-        <v>3.676299999999999</v>
+        <v>3.6763</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.6648000000000001</v>
+        <v>-0.6647999999999998</v>
       </c>
       <c r="W15" t="n">
         <v>10.7902</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>5.8298</v>
+        <v>5.9303</v>
       </c>
       <c r="E16" t="n">
-        <v>7.7346</v>
+        <v>7.8308</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.9048</v>
+        <v>-1.9004</v>
       </c>
       <c r="G16" t="n">
         <v>6.3981</v>
@@ -1702,13 +1702,13 @@
         <v>0.733</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.6677999999999999</v>
+        <v>-0.5673</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.5505</v>
+        <v>-0.4544</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.1173</v>
+        <v>-0.113</v>
       </c>
       <c r="V16" t="n">
         <v>-0.6335</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>5.2918</v>
+        <v>5.6473</v>
       </c>
       <c r="E17" t="n">
         <v>3.7434</v>
       </c>
       <c r="F17" t="n">
-        <v>1.5484</v>
+        <v>1.9039</v>
       </c>
       <c r="G17" t="n">
         <v>6.6534</v>
@@ -1780,13 +1780,13 @@
         <v>0.5498</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.995</v>
+        <v>-0.6395</v>
       </c>
       <c r="T17" t="n">
         <v>-0.3854</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.6097</v>
+        <v>-0.2542</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>4.9822</v>
+        <v>4.3396</v>
       </c>
       <c r="E18" t="n">
-        <v>5.5202</v>
+        <v>4.9433</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.538</v>
+        <v>-0.6036</v>
       </c>
       <c r="G18" t="n">
         <v>4.8569</v>
@@ -1858,13 +1858,13 @@
         <v>2.0158</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.0292</v>
+        <v>-0.6718</v>
       </c>
       <c r="T18" t="n">
-        <v>0.089</v>
+        <v>-0.4879</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.1182</v>
+        <v>-0.1839</v>
       </c>
       <c r="V18" t="n">
         <v>-0.945</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>C. GARCIA SAHUQUILLO</t>
+          <t>J. TORRES MARTINEZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.7504999999999999</v>
+        <v>1.0663</v>
       </c>
       <c r="E19" t="n">
-        <v>1.7883</v>
+        <v>0.5993000000000001</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.0378</v>
+        <v>0.467</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.8454</v>
+        <v>1.1756</v>
       </c>
       <c r="H19" t="n">
-        <v>1.0077</v>
+        <v>2.8426</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.8531</v>
+        <v>-1.667</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.4251</v>
+        <v>0.9379</v>
       </c>
       <c r="K19" t="n">
-        <v>0.6903</v>
+        <v>2.22</v>
       </c>
       <c r="L19" t="n">
-        <v>-1.1154</v>
+        <v>-1.2821</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.4204</v>
+        <v>0.2377</v>
       </c>
       <c r="N19" t="n">
-        <v>0.3173</v>
+        <v>0.6226</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.7377</v>
+        <v>-0.3849</v>
       </c>
       <c r="P19" t="n">
-        <v>0.1833</v>
+        <v>0.5498</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.9163</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.0995</v>
+        <v>0.5498</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.1763</v>
+        <v>-0.6591</v>
       </c>
       <c r="T19" t="n">
-        <v>0.2738</v>
+        <v>-0.6606</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.45</v>
+        <v>0.0015</v>
       </c>
       <c r="V19" t="n">
-        <v>1.5889</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>2.8559</v>
+        <v>0.3219</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.267</v>
+        <v>-0.3219</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>S. LOZANO CATALA</t>
+          <t>C. GARCIA SAHUQUILLO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.6828</v>
+        <v>0.8364</v>
       </c>
       <c r="E20" t="n">
-        <v>0.0433</v>
+        <v>1.6922</v>
       </c>
       <c r="F20" t="n">
-        <v>0.6394</v>
+        <v>-0.8557</v>
       </c>
       <c r="G20" t="n">
-        <v>0.6844</v>
+        <v>-0.8454</v>
       </c>
       <c r="H20" t="n">
-        <v>0.428</v>
+        <v>1.0077</v>
       </c>
       <c r="I20" t="n">
-        <v>0.2564</v>
+        <v>-1.8531</v>
       </c>
       <c r="J20" t="n">
-        <v>0.0433</v>
+        <v>-0.4251</v>
       </c>
       <c r="K20" t="n">
-        <v>0.0433</v>
+        <v>0.6903</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>-1.1154</v>
       </c>
       <c r="M20" t="n">
-        <v>0.641</v>
+        <v>-0.4204</v>
       </c>
       <c r="N20" t="n">
-        <v>0.3846</v>
+        <v>0.3173</v>
       </c>
       <c r="O20" t="n">
-        <v>0.2564</v>
+        <v>-0.7377</v>
       </c>
       <c r="P20" t="n">
         <v>0.1833</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-0.9163</v>
       </c>
       <c r="R20" t="n">
-        <v>0.1833</v>
+        <v>1.0995</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.1848</v>
+        <v>-0.09030000000000001</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>0.1776</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.1848</v>
+        <v>-0.2679</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.5889</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>2.8559</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-1.267</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>J. TORRES MARTINEZ</t>
+          <t>S. LOZANO CATALA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.5417</v>
+        <v>0.7076</v>
       </c>
       <c r="E21" t="n">
-        <v>0.5993000000000001</v>
+        <v>0.0433</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.0576</v>
+        <v>0.6642</v>
       </c>
       <c r="G21" t="n">
-        <v>1.1756</v>
+        <v>0.6844</v>
       </c>
       <c r="H21" t="n">
-        <v>2.8426</v>
+        <v>0.428</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.667</v>
+        <v>0.2564</v>
       </c>
       <c r="J21" t="n">
-        <v>0.9379</v>
+        <v>0.0433</v>
       </c>
       <c r="K21" t="n">
-        <v>2.22</v>
+        <v>0.0433</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.2821</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>0.2377</v>
+        <v>0.641</v>
       </c>
       <c r="N21" t="n">
-        <v>0.6226</v>
+        <v>0.3846</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.3849</v>
+        <v>0.2564</v>
       </c>
       <c r="P21" t="n">
-        <v>0.5498</v>
+        <v>0.1833</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>0.5498</v>
+        <v>0.1833</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.1837</v>
+        <v>-0.1601</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.6606</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.5231</v>
+        <v>-0.1601</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>0.3219</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.3219</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>V. MAS VIDAL</t>
+          <t>N. RAMON AÑIBARRO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>0.3418</v>
+        <v>0.3251</v>
       </c>
       <c r="E22" t="n">
-        <v>0.8464</v>
+        <v>0.3251</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.5046</v>
+        <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.6237</v>
+        <v>0.3251</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.7835</v>
+        <v>0.3251</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.8401999999999999</v>
+        <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.3059</v>
+        <v>0.3251</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.9727</v>
+        <v>0.3251</v>
       </c>
       <c r="L22" t="n">
-        <v>0.6667999999999999</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.3178</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>0.1891</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.5069</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>-1.0995</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>-2.7489</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1.6493</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>0.2092</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.2217</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>0.4309</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>2.8559</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>4.1229</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.267</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>N. RAMON AÑIBARRO</t>
+          <t>M. AROCA RUBIO</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>0.3251</v>
+        <v>0.1159</v>
       </c>
       <c r="E23" t="n">
-        <v>0.3251</v>
+        <v>1.1914</v>
       </c>
       <c r="F23" t="n">
-        <v>0</v>
+        <v>-1.0755</v>
       </c>
       <c r="G23" t="n">
-        <v>0.3251</v>
+        <v>2.3855</v>
       </c>
       <c r="H23" t="n">
-        <v>0.3251</v>
+        <v>3.9729</v>
       </c>
       <c r="I23" t="n">
-        <v>0</v>
+        <v>-1.5874</v>
       </c>
       <c r="J23" t="n">
-        <v>0.3251</v>
+        <v>4.0106</v>
       </c>
       <c r="K23" t="n">
-        <v>0.3251</v>
+        <v>3.8022</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>0.2084</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>-1.625</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>0.1707</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>-1.7958</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>-1.8326</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>-3.6651</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1.8326</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>-1.0705</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>-0.7534</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>-0.3172</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>0.6335</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.5993</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>-0.9658</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>M. AROCA RUBIO</t>
+          <t>V. MAS VIDAL</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.5747</v>
+        <v>0.0504</v>
       </c>
       <c r="E24" t="n">
-        <v>0.8068</v>
+        <v>0.6541</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.3814</v>
+        <v>-0.6037</v>
       </c>
       <c r="G24" t="n">
-        <v>2.3855</v>
+        <v>-1.6237</v>
       </c>
       <c r="H24" t="n">
-        <v>3.9729</v>
+        <v>-0.7835</v>
       </c>
       <c r="I24" t="n">
-        <v>-1.5874</v>
+        <v>-0.8401999999999999</v>
       </c>
       <c r="J24" t="n">
-        <v>4.0106</v>
+        <v>-0.3059</v>
       </c>
       <c r="K24" t="n">
-        <v>3.8022</v>
+        <v>-0.9727</v>
       </c>
       <c r="L24" t="n">
-        <v>0.2084</v>
+        <v>0.6667999999999999</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.625</v>
+        <v>-1.3178</v>
       </c>
       <c r="N24" t="n">
-        <v>0.1707</v>
+        <v>0.1891</v>
       </c>
       <c r="O24" t="n">
-        <v>-1.7958</v>
+        <v>-1.5069</v>
       </c>
       <c r="P24" t="n">
-        <v>-1.8326</v>
+        <v>-1.0995</v>
       </c>
       <c r="Q24" t="n">
-        <v>-3.6651</v>
+        <v>-2.7489</v>
       </c>
       <c r="R24" t="n">
-        <v>1.8326</v>
+        <v>1.6493</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.7611</v>
+        <v>-0.0822</v>
       </c>
       <c r="T24" t="n">
-        <v>-1.138</v>
+        <v>-0.414</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.6231</v>
+        <v>0.3318</v>
       </c>
       <c r="V24" t="n">
-        <v>0.6335</v>
+        <v>2.8559</v>
       </c>
       <c r="W24" t="n">
-        <v>1.5993</v>
+        <v>4.1229</v>
       </c>
       <c r="X24" t="n">
-        <v>-0.9658</v>
+        <v>-1.267</v>
       </c>
     </row>
     <row r="25">
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-1.7587</v>
+        <v>-1.2502</v>
       </c>
       <c r="E25" t="n">
-        <v>0.1865</v>
+        <v>0.5711000000000001</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.9452</v>
+        <v>-1.8213</v>
       </c>
       <c r="G25" t="n">
         <v>-3.0266</v>
@@ -2404,13 +2404,13 @@
         <v>0.9163</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.6142</v>
+        <v>-0.1058</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.6976</v>
+        <v>-0.313</v>
       </c>
       <c r="U25" t="n">
-        <v>0.0833</v>
+        <v>0.2072</v>
       </c>
       <c r="V25" t="n">
         <v>0.9658</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-3.1779</v>
+        <v>-3.1531</v>
       </c>
       <c r="E26" t="n">
         <v>-1.0164</v>
       </c>
       <c r="F26" t="n">
-        <v>-2.1615</v>
+        <v>-2.1367</v>
       </c>
       <c r="G26" t="n">
         <v>0.2008</v>
@@ -2482,13 +2482,13 @@
         <v>0.5498</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.4782</v>
+        <v>-0.4534</v>
       </c>
       <c r="T26" t="n">
         <v>-0.1652</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.313</v>
+        <v>-0.2883</v>
       </c>
       <c r="V26" t="n">
         <v>-2.5339</v>
@@ -2515,13 +2515,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-3.5389</v>
+        <v>-3.638</v>
       </c>
       <c r="E27" t="n">
         <v>-1.897</v>
       </c>
       <c r="F27" t="n">
-        <v>-1.6419</v>
+        <v>-1.741</v>
       </c>
       <c r="G27" t="n">
         <v>-0.3741</v>
@@ -2560,13 +2560,13 @@
         <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>-0.0653</v>
+        <v>-0.1644</v>
       </c>
       <c r="T27" t="n">
         <v>-0.2202</v>
       </c>
       <c r="U27" t="n">
-        <v>0.1549</v>
+        <v>0.0558</v>
       </c>
       <c r="V27" t="n">
         <v>-1.267</v>
@@ -2593,13 +2593,13 @@
         <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>9.695500000000001</v>
+        <v>10.9776</v>
       </c>
       <c r="E28" t="n">
-        <v>18.6805</v>
+        <v>18.6806</v>
       </c>
       <c r="F28" t="n">
-        <v>-8.985000000000001</v>
+        <v>-7.7028</v>
       </c>
       <c r="G28" t="n">
         <v>16.81</v>
@@ -2623,7 +2623,7 @@
         <v>-6.0039</v>
       </c>
       <c r="N28" t="n">
-        <v>2.334000000000001</v>
+        <v>2.334</v>
       </c>
       <c r="O28" t="n">
         <v>-8.337800000000001</v>
@@ -2638,13 +2638,13 @@
         <v>10.0792</v>
       </c>
       <c r="S28" t="n">
-        <v>-5.9464</v>
+        <v>-4.6644</v>
       </c>
       <c r="T28" t="n">
-        <v>-3.6764</v>
+        <v>-3.6765</v>
       </c>
       <c r="U28" t="n">
-        <v>-2.2701</v>
+        <v>-0.9883000000000001</v>
       </c>
       <c r="V28" t="n">
         <v>0.6647000000000003</v>
